--- a/光伏配储项目/电价数据/2026/润龙站.xlsx
+++ b/光伏配储项目/电价数据/2026/润龙站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.50979</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38213</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.6898099999999999</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.56272</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.4933</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.44057</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.43488</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43794</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45476</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.43935</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42328</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.41942</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.40895</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39856</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.40033</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38537</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40219</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42349</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41298</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35501</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39192</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38515</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41738</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39204</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42077</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41434</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42433</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.4131</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44433</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.35738</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.29988</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.33395</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.26081</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.29483</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.2973</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.19309</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.24495</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.06658</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.05536</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.03831</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.01684</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.03803</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.03798</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.03308</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>-0.01879</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.08527</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>-0.0227</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>-0.01819</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.00157</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.14459</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.21254</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.23515</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.18326</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.08982999999999999</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>-0.03465</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>-0.01042</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.09669</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.11411</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.1575</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.21018</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.14257</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.12079</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.10399</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.16842</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.18746</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.15601</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.34788</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.42272</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.35042</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.42703</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.33693</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.51837</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.32501</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.45703</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.72201</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.6085499999999999</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.48627</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0.45827</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>-0.04729999999999999</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.37271</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.5528999999999999</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.52425</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>0.1619</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.47994</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.48527</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.5814600000000001</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.5389400000000001</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.42328</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47874</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.40085</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41119</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.4202</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.33019</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.6075700000000001</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.39982</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.74002</v>
+      </c>
+      <c r="F118" t="n">
+        <v>0.94911</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.79963</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.53722</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.52408</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.5066700000000001</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.50331</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.50252</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.39264</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.47444</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.3722200000000001</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38123</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39249</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.3379</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37168</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35715</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.36032</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.37662</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37654</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.36054</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.38148</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.42305</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.5169600000000001</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.6298899999999999</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.7223099999999999</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.43759</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.35262</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.38349</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34565</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.32153</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.31624</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.43443</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.07545</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.30721</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.29105</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.251</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.29439</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.25945</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.26408</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.3112200000000001</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.21928</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.34679</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.57724</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.02567</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.26822</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.25482</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.28126</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.28694</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.2258</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.5532999999999999</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.37129</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.34336</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>-0.04404</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.27067</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.29879</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.30275</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.29674</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.30426</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.2856</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.21353</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.15273</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.2166</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.21905</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.23036</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.24956</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.39339</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.39788</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.28956</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.21121</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.32002</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.29216</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>0.39479</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.20078</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.68596</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.79479</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.78703</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.18523</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.3002</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.80276</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.28755</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.35877</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>0.7496799999999999</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.27537</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.43539</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.59028</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.43883</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43307</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.40676</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33265</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37549</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35246</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33291</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.3216</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.51577</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.36916</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.46779</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.36266</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.38063</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.40139</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.3837</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.39062</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38034</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.35998</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43257</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44869</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33499</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37129</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39254</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36328</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.36995</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35175</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.35703</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.34676</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36098</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35456</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.37764</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39646</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47404</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44832</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.4427</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34807</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39557</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35241</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36763</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34564</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.27129</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.28277</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.27857</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.30691</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.12386</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.27246</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.24682</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.30318</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.30709</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.29243</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.28058</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.33534</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.39453</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.34587</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.3791600000000001</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.22768</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.38785</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.24254</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.279</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.0528</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.19727</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.12422</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.18434</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.17319</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.24136</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.29194</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.33509</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.29871</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.2794700000000001</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.31798</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.30848</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.25195</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.29345</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.25158</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.20175</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.15542</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.26348</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.29949</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.30068</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.31525</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.32327</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.44969</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.48135</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.30981</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.28159</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.27744</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.245</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.29619</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.25669</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.35858</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.37929</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.36543</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.2798</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.29439</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.30771</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.29814</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.34383</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.34054</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.33572</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34988</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34341</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.32019</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.28685</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.34445</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.3299</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.31719</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.34479</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.33422</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.32693</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.32711</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.29984</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.29981</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.47052</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.31129</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.31815</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.29991</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.3158</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.3165</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.2954</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.29751</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.29435</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.29322</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.29478</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.33894</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33923</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.36025</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.3406</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.39027</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.31755</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.31675</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.33812</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.3035</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.28094</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.26304</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.20124</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.12074</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.11352</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.08452</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.26459</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.22611</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.11101</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.28507</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.4391</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.28862</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.37175</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.19057</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.06365999999999999</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.25441</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.20183</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.03647</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>-0.03055</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.25567</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>-0.01348</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.02814</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.05479999999999999</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.09153</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.35358</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.31799</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.24985</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.19318</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.22216</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.18035</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.22976</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.16075</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.23408</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.25075</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.28935</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.33439</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.31188</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.33681</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.26046</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.27904</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.2875</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.41978</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.48392</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.40804</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.39403</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.3218</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.31924</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.3267</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.33632</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.30909</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.31164</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.30652</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.27689</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.30681</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32032</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.29422</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.29001</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.29996</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.28799</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.29105</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.29728</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.32191</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.33761</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.33666</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.32089</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.30122</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.31098</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.30975</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.30137</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.3024</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.28364</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.30126</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.29949</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.28279</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.28626</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.29018</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.29018</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.29023</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.29214</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.29515</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31235</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.30386</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31648</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32435</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32427</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33285</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32606</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.27934</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.26052</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.04017</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.04532</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.03994</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.03979</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.04296</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.04614</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.04451</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.04654</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>-0.04212</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>-0.04654</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>-0.04617</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>-0.04455</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>-0.0447</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>-0.04571</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>-0.04465</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>-0.0436</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.046</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.04918</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>-0.04507</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.0458</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.04724</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.04714</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.04949</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>-0.04506</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>-0.04697</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.22031</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.04728</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.05119</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.05339</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>-0.00256</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.1465</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.03692</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.09845000000000001</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.28968</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29185</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.29303</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31984</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.3294</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31426</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33492</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33114</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.32338</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.37437</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.38795</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.38281</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.37785</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34128</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.40072</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39712</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.41203</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46765</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35386</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39654</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.40016</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.4176</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35505</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35811</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34528</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35518</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.35139</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36802</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.66362</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.40013</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.4466</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.4238</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.42388</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.35996</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.35938</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.35912</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.33471</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.3103399999999999</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.32569</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.35797</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.35663</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.3487</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.3475</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33507</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.31551</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.33031</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.3356</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.32279</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.30015</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.32287</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33542</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.33912</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35031</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35212</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34295</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31619</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10242</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04247</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04627000000000001</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04576</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04531</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04532</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04531</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04454</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04255</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.03197</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>-0.04134</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.10656</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.00046</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.03765</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>-0.04706</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.04206</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04216</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04206</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04436</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04427</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04426</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04202</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04146</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04397</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04127</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.03979</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04488</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04399</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04428</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04182</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04286</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>-0.04047</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>-0.04295</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.0499</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04373</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.04683</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04671</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.20151</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14409</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.2918</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29654</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30639</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.30162</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29668</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29406</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29527</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29433</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29881</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29249</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29652</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.27049</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29546</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29961</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30959</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30583</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30287</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31628</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.32028</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34945</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.35153</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34639</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36844</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.3669</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33702</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33209</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.32088</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31233</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.4064700000000001</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.35173</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32233</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30986</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31628</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30309</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28276</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29696</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29266</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28974</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.2828</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27273</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27271</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.28258</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17365</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1599</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17247</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14896</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.16068</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15999</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23844</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21541</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22796</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.27111</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28757</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29234</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.32099</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.29264</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.2828</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28262</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28236</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.26945</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28239</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32443</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31216</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30687</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.31807</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.31038</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.36012</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31324</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.26684</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.37493</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.38125</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.41743</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.42411</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.32912</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.40675</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.4035899999999999</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.38992</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.39362</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.29977</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30098</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29877</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.30007</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15735</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.28131</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.30844</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31087</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.30575</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32189</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34091</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30044</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.3298</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38095</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.50747</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79111</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6218899999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.39985</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49776</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.78083</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.91995</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49424</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.92336</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.89303</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.31162</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.38243</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.916</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63627</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.21504</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.88248</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.56631</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.35959</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.0526</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.5597000000000001</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.81562</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.53084</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.79774</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.79718</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.87982</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.88681</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.5162899999999999</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.42125</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.42962</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.47637</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.23672</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.8796799999999999</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.5515399999999999</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.65132</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.54567</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.50617</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45942</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42772</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.44234</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45134</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.39562</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45306</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42153</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35566</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.40031</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36552</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.39292</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41517</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.4342200000000001</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34421</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39114</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.35083</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.36409</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.35994</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.36077</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.41023</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.36235</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45114</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35779</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.39987</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.40058</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.58873</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.42842</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59662</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.60158</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.6555</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.45174</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.40494</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.5548500000000001</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.44643</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.8620800000000001</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.66265</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.82912</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>0.8121499999999999</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.84709</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.32476</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.43257</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.32475</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30199</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.28038</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.4179</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.29352</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.27124</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.30654</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35837</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33245</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.31959</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.33924</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.33983</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31777</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.30623</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31908</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31975</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.34431</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.31475</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.31488</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32069</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.31634</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.32762</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.3124</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.31389</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.3152799999999999</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.30986</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.31642</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.32307</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.32457</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.32635</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.35555</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.34198</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.34017</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33892</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.33064</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.33744</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.33556</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.41033</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41304</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45288</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.4154</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.39184</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.37529</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35338</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.33005</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.98853</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36084</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.48786</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.45286</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.54755</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.61586</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.40338</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.41003</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.41937</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.4609</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.4142</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.35937</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.38839</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33085</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35951</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.3460299999999999</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32326</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.40052</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.50073</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.35747</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.388</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34379</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35116</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.35554</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37085</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35768</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36283</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31335</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33237</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33793</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33795</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.34948</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.31536</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.30262</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29047</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.30336</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.28893</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.27781</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.16457</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.28127</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30789</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.32953</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.30374</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.31177</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.29681</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.26084</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.20056</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.2775</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.25774</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.34973</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.27502</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.31283</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.31898</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.3417</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.35893</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.32098</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.3126</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.31984</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.30506</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.31301</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.28982</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.30226</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.29113</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.30915</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.32046</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.3116</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.28988</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.3475</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.2554</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35021</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32215</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.26862</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.35249</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27544</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.34932</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32885</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.33849</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.31006</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.34938</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.31628</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.38541</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.32269</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.4318</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.2762</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42323</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.35058</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44774</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.31772</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42076</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35908</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40207</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40081</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.59782</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35053</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.88967</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.35081</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.14033</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.7075</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.80031</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.65227</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.58778</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.4512</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45042</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.50054</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.43997</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43773</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41512</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41299</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42377</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.5010899999999999</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41299</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43414</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41328</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43418</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39047</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42845</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.4509</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39638</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.42355</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43455</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41299</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41296</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.40061</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42398</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.39636</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.40282</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.5644</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.37377</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.35577</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.29748</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.36974</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.36292</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.30092</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.33268</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.30068</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.3189</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.31016</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>0.0668</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.49616</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.34243</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.32358</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.24994</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.04009</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.6745099999999999</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.21958</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.32825</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.31135</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.35763</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.55055</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30435</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.26579</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.26649</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.29737</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.26577</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.28946</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.38453</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.29448</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.34289</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.29455</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.3082</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.31952</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.31437</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.33833</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.38578</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.34683</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.35925</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.33961</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.33532</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.37271</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.43942</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.35996</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.40671</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.36409</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.35248</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.5872000000000001</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.46452</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.7142999999999999</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.46585</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.4387200000000001</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.37616</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.42466</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38744</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.37052</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33547</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.34176</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.3304</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32572</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31946</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.42474</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.34055</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.34542</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.3414</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33691</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32748</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.33074</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32754</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32622</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32555</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.31121</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.32844</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32727</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.32088</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31694</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.3214</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.32138</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.31097</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32589</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.31195</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.32112</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.32165</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.39298</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32701</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.35108</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.40148</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37632</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.35085</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.3396</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.35599</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33413</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.31899</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.25913</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.33211</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.32073</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.26752</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.30535</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.29209</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.2359</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.14501</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.14734</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.29646</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.1542</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.1444</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.14085</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.14418</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.14266</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.25746</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.14472</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.26681</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.26718</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.14219</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.03504</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.11418</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.11328</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.14547</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.14153</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.14671</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.28743</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.32396</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.3303</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.32179</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.34567</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31667</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.35605</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.34897</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.38088</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34407</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.38065</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.34673</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.3991</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.36136</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38567</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.45084</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.4007</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.39324</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40292</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.3988</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.44089</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.44109</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.44048</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.44542</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44487</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.4035</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.39125</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39842</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.39219</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.36056</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.36126</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34892</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.35011</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.34044</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.5519400000000001</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38974</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46977</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42481</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41685</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37048</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38195</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.38122</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.39399</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.38069</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.37016</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.38067</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.36042</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.39155</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.37062</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.38072</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.35056</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34756</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35557</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34517</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.34049</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.34551</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.3405</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34512</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35585</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.3706</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.38043</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.36019</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.34048</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.3404700000000001</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.33164</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34684</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.35666</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.40486</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.26771</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.30906</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.30881</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30244</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.26366</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.27291</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.23769</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.23321</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.1818</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.2744</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.23807</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.2155</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.24013</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.29033</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.27215</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.30823</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.26146</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.28523</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.28876</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.27925</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.28216</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.26977</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.21555</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.30231</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.27417</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.29645</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.27215</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.25679</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.31396</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.33662</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.34138</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.32647</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.32015</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.30702</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.32076</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.3303</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.34787</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.36446</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.36487</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.37846</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.41406</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.42144</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.24399</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.39531</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.38247</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.35459</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.35719</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.35486</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41808</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.44803</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.34819</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.36755</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.37049</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.36042</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.38074</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38053</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38568</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.35039</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.36055</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.3403</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36644</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.42002</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37081</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.39193</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.38098</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35298</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34977</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.36058</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35196</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34221</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34797</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34598</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34731</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.34088</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.34242</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34341</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33878</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33856</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.34027</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.34139</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.3325</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.35053</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.3445</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.36171</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.31315</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.32897</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.33945</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.32574</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.31808</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33123</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.32006</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.30936</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.35214</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.33103</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.28046</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.36893</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.40646</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.29536</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.38894</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.27334</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.26508</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.33376</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>-0.03997999999999999</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.24906</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.24994</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.19548</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.07012</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.17743</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.244</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.28446</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.31114</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.26627</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.24812</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.2844</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.29805</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.29251</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.26745</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.29285</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.32658</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.32253</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.32091</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.40951</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.3313</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.32454</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.33265</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.34181</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.30203</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.37623</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.3092200000000001</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.31343</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.31825</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.32783</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.31981</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.46999</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.40262</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.7313999999999999</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.35185</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.40771</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.34621</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.33054</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.33886</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.4495</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.35432</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.40513</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.29826</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.34275</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.34519</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.34583</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.31737</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.31098</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.31821</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.30115</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.3379</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30495</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.34136</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.33104</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.32847</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.3254</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.33036</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.32526</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.32555</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.32479</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.32397</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.32659</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32458</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32748</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32878</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32734</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32767</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32421</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33131</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.32648</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32113</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31981</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.3231</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32652</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.33114</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33546</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34656</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.3411</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.34119</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33907</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.32154</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.3213</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33446</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.34984</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.35431</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.33433</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.32428</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.31833</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.31614</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32334</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.31592</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.33719</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.27804</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.34176</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34062</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.28923</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32577</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28181</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.32477</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.31865</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.31962</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.32566</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32867</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33322</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.33097</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.3132799999999999</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.32666</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.31952</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.32011</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.31996</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.31348</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.34908</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.30315</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.28354</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.31408</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.34307</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.32263</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.34063</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.33145</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35012</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35016</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35017</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.36012</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.32631</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.32948</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.34772</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.3782</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.36924</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.36375</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.37017</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.36459</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.37539</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.36291</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.39647</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38576</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37168</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.40449</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35505</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.38068</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.37182</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36127</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35062</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.3501</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.34995</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34924</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.33989</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35195</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.3576</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35708</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35173</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.3509</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.3501</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34988</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34975</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34658</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.36093</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34739</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.35069</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34991</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33716</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33988</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.33995</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.36994</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32444</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.33865</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33988</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.34992</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33698</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.3451</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.3362</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.3499</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.3499</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.3366</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34022</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.32828</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34895</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.33995</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.33177</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.33628</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.28104</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.32635</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32769</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.32865</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32543</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.31842</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.32734</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31851</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.32862</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32877</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31907</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37088</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.32039</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.31778</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.31537</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32377</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.32152</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32721</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32128</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.32289</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.32966</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.33016</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33172</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33603</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34572</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.35846</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.6045900000000001</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.39311</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35476</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35523</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.36663</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.35067</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.36025</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34748</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.36059</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.36051</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36255</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.35049</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.3791600000000001</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.38045</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.38163</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38305</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.42393</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.40518</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.38569</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.38628</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.61613</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.78115</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.46304</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.41918</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.44976</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.39203</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.35094</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35084</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.3599</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.3400899999999999</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34504</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.31725</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.40546</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37511</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37079</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36342</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35993</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36286</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35956</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.36099</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35985</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35376</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36079</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36096</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35705</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35245</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35993</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.36027</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35991</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.34364</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37105</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35883</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35655</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36013</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36013</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.37794</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36581</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.37802</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35657</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35653</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35117</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35186</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35846</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.31989</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.33134</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.32133</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.26051</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.13342</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.2891</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.2839</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.28238</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.19451</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.24416</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.27827</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>-0.02277</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.27955</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.11533</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>-0.02335</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.28387</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.23058</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.28697</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.24037</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.30281</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.30225</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.14374</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.29619</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.20864</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.21637</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.28302</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.28547</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.29567</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.29292</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.30116</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.2893</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.30857</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.33107</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.33875</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.33698</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.29405</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.33899</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.41446</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.36321</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.3985</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.6137100000000001</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.58323</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.5779</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.45218</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.5946900000000001</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.45956</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.68031</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.43629</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.44361</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.39561</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.3746</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.3554</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.46435</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.42188</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.41249</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.37708</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37363</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36709</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.36023</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34587</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.47596</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.4468</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.44729</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.43629</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.41433</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.39686</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40224</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.40814</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.40604</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.41325</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.39785</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.39453</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.40827</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.40619</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.39209</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38668</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.4136</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.38683</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41193</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.38864</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.39725</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.39719</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.40825</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.3971</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.4411600000000001</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.44025</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.53684</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.48445</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.44127</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.36565</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.41408</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.36111</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.32122</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.36803</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.37268</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.42687</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.36095</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.38455</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.31893</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.28726</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.31441</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.33516</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.36751</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.35627</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.37103</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.28616</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.23758</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.26306</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.12402</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>-0.00537</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>-0.01615</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.29414</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.29603</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.6746799999999999</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.34818</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.26266</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.1152</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.07984000000000001</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>-0.04986</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.25227</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>-0.01195</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.32743</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.32398</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.31296</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.32629</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.3469100000000001</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.32714</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.33778</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.3304</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.3391</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.33533</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.32297</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.34996</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.40605</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.46978</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.41991</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.49026</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.49146</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.40014</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.54647</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.6423300000000001</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.6383300000000001</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.61726</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.70147</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.51091</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.50434</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.7607999999999999</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.7041799999999999</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.57455</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.61778</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.40194</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.42773</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.46805</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.46567</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.4602</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.41398</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.51068</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.41644</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.43491</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.44796</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.42924</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42014</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.4393</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41268</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.39789</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.44743</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39665</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.4034</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39625</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38738</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.3799</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37525</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36012</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35692</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.3659</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37738</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.3714</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.36032</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35998</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.3659</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38565</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.38865</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37943</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36672</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36153</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35524</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37987</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.39971</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.36702</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.388</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.39024</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.34361</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38527</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.3517</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.36837</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.34316</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.32518</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.26785</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.28645</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.15327</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.3389</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.26284</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.3474100000000001</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.03545</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.3049</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.35165</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.40878</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.3797</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.45515</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.41441</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.46585</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.3144</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.30954</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>-0.03468</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.1844</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.30337</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29278</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.31783</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35285</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.35036</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.34835</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.34849</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.36462</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.36551</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.35757</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.39806</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.40815</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.36248</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.40835</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.39767</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.39004</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.36993</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.35393</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.37764</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.3849</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.40239</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.39827</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34384</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.36441</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37832</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.40005</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36012</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.37977</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35512</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.3998</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.38083</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37511</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.36067</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39376</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.37895</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.364</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.33161</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.44361</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.35629</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.37488</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.37535</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.35593</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.37699</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.35098</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.37715</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.36538</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.35614</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35403</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.35171</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.35752</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34786</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.35042</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.34864</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.3398</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33173</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.33992</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.3406</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33574</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.34075</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34576</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.33141</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.33076</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.33938</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.33948</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.34566</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.32688</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.31787</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.31215</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.32599</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.24011</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.32793</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.32246</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.31685</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.23265</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.23412</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.23423</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.2477</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.00239</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.13057</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.2308</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.28789</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.00996</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.15976</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04343</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.25615</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>-0.00484</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.14505</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.15324</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.02944</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.30317</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>-0.04084</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.21531</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.22554</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.14851</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.21044</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.26489</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28351</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.25762</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.29538</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.32604</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.28498</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.3494</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.34636</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.34987</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.34864</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.34779</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.32578</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.33096</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.35856</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.34882</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.34346</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.30886</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.34979</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.35454</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.36548</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.35311</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.35945</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.36362</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.35792</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.34478</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.35901</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.37163</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.34336</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.36621</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.37095</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.35052</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.35085</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.35036</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.35083</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.35226</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.32342</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.33897</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.34293</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.33897</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.34016</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.33235</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.32581</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.3207</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.32035</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.31137</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.3108</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.31562</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.3108399999999999</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.3118</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.31161</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.31144</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.30744</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.30744</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.30994</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.31102</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.30679</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.30744</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.30806</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.3108399999999999</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.31204</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.29158</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.2255</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.21559</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.15025</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.17878</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.0469</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.01586</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>-0.00183</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.0435</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.05609</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>-0.03421</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.04181</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>-0.03511</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.04506</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.04877</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.03484</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.16834</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.21377</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.27644</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.24351</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.24477</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.24524</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.24965</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.26246</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.28588</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.27112</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.26749</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.2561</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.30324</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.27572</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.27935</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.26417</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.27894</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.26668</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.28279</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.27257</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.29207</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.35959</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.29934</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.30363</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.28387</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.25363</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.26547</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.2497</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.23269</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.17559</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.05201</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29794</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.40174</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.00377</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.06031</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.24523</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.22227</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.22195</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.13961</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.26812</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.25949</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.24185</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.21962</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.20408</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.18704</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.21107</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.22438</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.16715</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.18692</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.22169</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.21738</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.2428</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.23006</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.21313</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.25976</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.22334</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.26699</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.32564</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.26913</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.24503</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.24785</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.18176</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.06014</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.48533</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.49319</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.53899</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.36644</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.06708</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.22086</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>-0.02779</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.20015</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.09046999999999999</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.03920000000000001</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.05176</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>-0.01107</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.20713</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.02855</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.28962</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.00547</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.02334</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.12874</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.03929</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.03723</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.02629</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.07836</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.02261</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.009310000000000001</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.02417</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.04429</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.23173</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.27869</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.249</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.27677</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.30239</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.30429</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.30063</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.3171</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.32119</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.30878</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.31456</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.32703</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.31988</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.3404</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.33954</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.34679</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.16549</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.34113</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.34094</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.33429</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0.34912</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.34069</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.3667</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.32903</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.3410899999999999</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.34987</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.31923</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.32894</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.32976</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.33093</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.32803</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.33998</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.32531</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33022</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.35519</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.36714</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.33323</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.33639</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.33562</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.33096</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.33099</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.33123</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.33374</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.32926</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.34187</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.33514</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.33437</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.32771</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.3446</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.11081</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.32663</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.32716</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.32127</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.33145</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.32883</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.32963</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.3321</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.3357</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.3433</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.23168</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.38783</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.2363</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.29859</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.24048</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.11479</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.23083</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.35151</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.28571</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.30633</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.38783</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.30542</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.39158</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.32334</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.31343</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.3382</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.29647</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.3088399999999999</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.30664</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.30815</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.28987</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.1105</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.25341</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.2697</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30388</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.31069</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.16675</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.31868</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.14847</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.07293000000000001</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.3088399999999999</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.29004</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.31023</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.3164</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.32088</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32643</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.33676</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32379</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.34701</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.34014</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.33767</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.33887</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.34016</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.34478</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33118</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.3477</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.34636</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.33356</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.34342</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.3394</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.34339</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.37167</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.31581</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.30912</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.3574</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.38024</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.34034</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.35127</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.34679</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.35235</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.34611</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.36805</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.35247</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.31473</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.33213</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.3261</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.33093</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.3312</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.37065</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.33108</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.33107</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.26225</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.31652</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.32024</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.32822</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.32935</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.33077</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.33185</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.33563</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.3452</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.28704</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.3494</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.34083</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.33628</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.32106</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.32077</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.33129</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34662</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33124</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.34034</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.35416</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.32335</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36949</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.35543</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.36976</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35952</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.34713</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.26146</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.33008</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.34043</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.33602</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.49615</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.2803</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.50317</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.23706</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.28514</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.3075</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.34276</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.28573</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.25935</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.27988</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.27051</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.25471</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.13465</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.2552</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.30772</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.36737</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.2777</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.25351</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.25688</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.28581</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.34468</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.34775</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32676</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.23136</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.27126</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.31621</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.29916</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.26493</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.26672</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.28842</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.34478</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.41636</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.3981</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.46396</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.47685</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.45816</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.47376</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.37671</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>-0.0418</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.37288</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.40325</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.43411</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.31499</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.39646</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.34258</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.47207</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.43198</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.37257</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.41727</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.42594</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.74612</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.45132</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.4074700000000001</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.45932</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.40175</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.37981</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.38758</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.36735</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.36725</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37276</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.36858</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.36898</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34706</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.46568</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.40036</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.40043</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.39076</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.38083</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36022</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37569</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37452</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37874</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.37746</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36929</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36698</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36161</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36005</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.3599</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.36045</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32915</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35624</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35129</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.34987</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.3473</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.35017</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.3604</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37127</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.40009</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.37604</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.36938</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.34916</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.33672</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.28512</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.33612</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.29298</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.29631</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.27437</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.37297</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.31535</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.284</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.34375</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.18278</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.32882</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.15185</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.34133</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.22923</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.34799</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.33093</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.33145</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29228</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.28827</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.30633</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.3099</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.25213</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31951</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33806</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.33229</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.17385</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.28745</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.25215</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.26045</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.30118</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.30425</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.30795</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.33841</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.32741</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.34237</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.32497</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.35792</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.43048</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.35716</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.40427</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.3882</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.38472</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.45888</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.55649</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.55259</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.3788</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.45781</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.5466599999999999</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.45803</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.34814</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.49012</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.39407</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.5308200000000001</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.52151</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.72763</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.76935</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.54471</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.54686</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39867</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.44334</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.38804</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.37423</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.37943</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.37001</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37568</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.27325</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.36989</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.31871</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.37132</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.33516</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.3381</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.35079</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.32106</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.33504</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.34377</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.33888</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.33976</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.34512</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.33584</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.33772</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.33633</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.31385</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.3277</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.31968</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.30924</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.30441</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.30849</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.30902</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.29163</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.29098</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.34514</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.36327</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.30336</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.28957</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.28496</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.27929</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.27274</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.3132799999999999</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.2578</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.25725</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.27352</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.20739</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.23179</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.13267</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>-0.02249</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.13663</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.00899</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.09779</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>-0.01421</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>-0.0413</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>-0.02509</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.23347</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>-0.04173</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.01978</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.03293</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.02366</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.01033</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.01184</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.02764</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.11917</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.06282</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.12863</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.14217</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.17358</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.24174</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.18813</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.15637</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.32649</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.29332</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.30739</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.30993</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.34148</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.22197</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.33329</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.27021</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.36363</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.38483</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.35731</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.36632</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.3364</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.39333</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.3757</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.37477</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.40021</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.38132</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.36067</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.35089</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.35939</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.41385</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.3791600000000001</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.3757</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.37591</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.38812</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.3784</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.35299</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.8017000000000001</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.34057</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.39937</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.37765</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.33544</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.33851</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.3538</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.35196</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.3834</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.34574</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.34702</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.34225</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.38151</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.35537</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.36204</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.3804</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.37917</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.34783</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.36097</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.36374</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.36181</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.36523</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.35595</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.36698</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.35222</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.36612</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.34056</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.32024</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.32317</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.30296</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.30286</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.29561</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.28933</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.27544</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.25267</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.24324</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.21372</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.21333</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.21746</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.23901</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.08139</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.00574</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.00298</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.00231</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.0351</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.11116</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.02498</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>-0.00347</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.01325</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.01348</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.01324</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.02127</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.15725</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.1726</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.02761</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.15961</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.133</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.14832</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.17357</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.11641</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.20485</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.19061</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.23983</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.22188</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.27011</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.30169</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.28346</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.42195</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.37785</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.39442</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.36138</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.38601</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.40374</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.35614</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.35692</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.38284</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.5204099999999999</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.4108</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.38567</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.39212</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.39328</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.388</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.38248</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.40346</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.35495</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.38719</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.42688</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.3854</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.38808</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.38058</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.38468</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.37418</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.36244</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.38686</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.32899</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.5186799999999999</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.39238</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.39559</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.31489</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.36989</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.36627</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.34628</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.4196</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.34495</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.37649</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.3732799999999999</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.3424</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.34101</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.33344</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.31667</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.35032</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.32336</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.32044</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.33285</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.36451</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.34015</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.35395</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.3407</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.3416</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.32324</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.29149</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.25388</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.21737</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.19824</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.12745</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.17549</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.20242</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.19569</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.1024</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.12612</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.0523</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.08395</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.03632</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.03736</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.03718</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.03578</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.04606</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.05312</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.06786</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.03594</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.06203</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.08452</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.1397</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.17716</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.10195</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.20581</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.18137</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.10575</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.04801</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.23513</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.11959</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.10485</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.20938</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.15649</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.17593</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.20299</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.17284</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.21033</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.23366</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.23463</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.2502</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.27604</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.28014</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.28237</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.3596</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.39262</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.33948</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.32653</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.29516</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.34676</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.38453</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.37311</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.37639</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.36409</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.38552</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.4079</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.41401</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.49276</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.40491</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.41322</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.43084</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.41108</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.39247</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.4086</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.40975</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38404</v>
       </c>
     </row>
   </sheetData>
